--- a/docs/tech/ezSyncServer/인사연동_뷰테이블_정의서.xlsx
+++ b/docs/tech/ezSyncServer/인사연동_뷰테이블_정의서.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Projects\kaoni\jmocha\ezFlow4Java\docs\tech\ezEKP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Projects\kaoni\jmocha\ezFlow4Java\docs\tech\ezSyncServer\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -16,12 +16,12 @@
     <sheet name="사용자" sheetId="2" r:id="rId2"/>
     <sheet name="겸직" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" iterateDelta="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="89">
   <si>
     <t>부서 TABLE</t>
   </si>
@@ -1214,7 +1214,9 @@
       <c r="C22" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D22" s="1"/>
+      <c r="D22" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1" t="s">
         <v>43</v>
@@ -1459,8 +1461,12 @@
       <c r="C11" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
+      <c r="D11" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="F11" s="1" t="s">
         <v>29</v>
       </c>
